--- a/Testdaten/Testdaten von und für GPT-4o/OpenCart-Testfälle GPT-4o.xlsx
+++ b/Testdaten/Testdaten von und für GPT-4o/OpenCart-Testfälle GPT-4o.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marvi\Desktop\Bachelor-Thesis\Testdaten\Testdaten von und für GPT-4o\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF8E6AE-CBE4-4020-BE6C-56476E376C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA70234-C9A3-4488-A833-0A536D5147EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,22 +22,8 @@
     <sheet name="My Account" sheetId="12" r:id="rId7"/>
     <sheet name="My Account Information" sheetId="13" r:id="rId8"/>
     <sheet name="Change Password" sheetId="14" r:id="rId9"/>
-    <sheet name="Address Book" sheetId="15" r:id="rId10"/>
-    <sheet name="Order History" sheetId="16" r:id="rId11"/>
-    <sheet name="Order Information" sheetId="17" r:id="rId12"/>
-    <sheet name="Product Returns" sheetId="18" r:id="rId13"/>
-    <sheet name="Downloads" sheetId="19" r:id="rId14"/>
-    <sheet name="Reward Points" sheetId="20" r:id="rId15"/>
-    <sheet name="Returns" sheetId="21" r:id="rId16"/>
-    <sheet name="Transactions" sheetId="22" r:id="rId17"/>
-    <sheet name="Recurring Payments" sheetId="23" r:id="rId18"/>
-    <sheet name="Affiliate" sheetId="24" r:id="rId19"/>
-    <sheet name="Newsletter" sheetId="25" r:id="rId20"/>
-    <sheet name="Contact Us" sheetId="26" r:id="rId21"/>
-    <sheet name="Gift Certificate" sheetId="27" r:id="rId22"/>
-    <sheet name="Specail Offers" sheetId="28" r:id="rId23"/>
-    <sheet name="Header Menu Footer Options" sheetId="29" r:id="rId24"/>
-    <sheet name="Currencies" sheetId="30" r:id="rId25"/>
+    <sheet name="Order History" sheetId="16" r:id="rId10"/>
+    <sheet name="Currencies" sheetId="30" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="531">
   <si>
     <t>Validate the My Account functionality</t>
   </si>
@@ -71,40 +57,7 @@
     <t>Validate the working of My Account &gt; 'Change Password' functionality</t>
   </si>
   <si>
-    <t>Validate the working of My Account &gt; 'Address Book' functionality</t>
-  </si>
-  <si>
     <t>Validate the working of My Orders &gt; 'Order History' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of My Orders &gt; 'Order Information' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of My Orders &gt; 'Product Returns' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of My Orders &gt; 'Downloads' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of My Orders &gt; 'Reward Points' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of My Orders &gt; 'Returned Requests' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of My Orders &gt; 'Your Transactions' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of My Orders &gt; 'Recurring Payments' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of 'Affiliate' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of 'Newsletter' functionality</t>
-  </si>
-  <si>
-    <t>Validate the working of 'Contact Us' page functionality</t>
   </si>
   <si>
     <t>Number of Test Cases</t>
@@ -1720,6 +1673,208 @@
   </si>
   <si>
     <t>The system displays an error message: 'Password must be greater than 3 and less than 20 characters!'</t>
+  </si>
+  <si>
+    <t>TC_OH_001</t>
+  </si>
+  <si>
+    <t>Access Order History page</t>
+  </si>
+  <si>
+    <t>Verify user can access the Order History page</t>
+  </si>
+  <si>
+    <t>1. Navigate to OpenCart.
+2. Log in with valid credentials.
+3. Click on 'Purchases' in the sidebar.
+4. Click on 'Your Orders'.</t>
+  </si>
+  <si>
+    <t>The Order History page is displayed successfully.</t>
+  </si>
+  <si>
+    <t>TC_OH_002</t>
+  </si>
+  <si>
+    <t>No previous orders</t>
+  </si>
+  <si>
+    <t>Open OpenCart
+User is logged in
+User has no past orders</t>
+  </si>
+  <si>
+    <t>Verify empty order history</t>
+  </si>
+  <si>
+    <t>1. Navigate to 'Your Orders' page.
+2. Check if any orders are listed.</t>
+  </si>
+  <si>
+    <t>The system displays 'No results!' if there are no past orders.</t>
+  </si>
+  <si>
+    <t>TC_OH_003</t>
+  </si>
+  <si>
+    <t>Existing orders are displayed</t>
+  </si>
+  <si>
+    <t>Open OpenCart
+User is logged in
+User has past orders</t>
+  </si>
+  <si>
+    <t>Verify order details are shown</t>
+  </si>
+  <si>
+    <t>1. Navigate to 'Your Orders' page.
+2. Check if past orders are listed with correct details (ID, Extension Name, Amount, Status, Add Date, Action).</t>
+  </si>
+  <si>
+    <t>All past orders should be displayed correctly with the following details: ID, Extension Name, Amount, Status, Add Date, Action.</t>
+  </si>
+  <si>
+    <t>TC_OH_004</t>
+  </si>
+  <si>
+    <t>Filter orders by date</t>
+  </si>
+  <si>
+    <t>Verify filtering functionality</t>
+  </si>
+  <si>
+    <t>1. Navigate to 'Your Orders' page.
+2. Apply a date filter (if available).
+3. Check if only orders within the selected range are displayed.</t>
+  </si>
+  <si>
+    <t>The system correctly filters and displays orders within the selected date range.</t>
+  </si>
+  <si>
+    <t>TC_OH_005</t>
+  </si>
+  <si>
+    <t>Click on an order</t>
+  </si>
+  <si>
+    <t>Verify user can view order details</t>
+  </si>
+  <si>
+    <t>1. Navigate to 'Your Orders' page.
+2. Click on an order ID or 'Action' button.</t>
+  </si>
+  <si>
+    <t>The system navigates to the order details page.</t>
+  </si>
+  <si>
+    <t>TC_OH_006</t>
+  </si>
+  <si>
+    <t>Slow loading orders</t>
+  </si>
+  <si>
+    <t>Open OpenCart
+User is logged in
+User has many past orders</t>
+  </si>
+  <si>
+    <t>Verify performance with many orders</t>
+  </si>
+  <si>
+    <t>1. Navigate to 'Your Orders' page.
+2. Observe loading time when multiple orders are displayed.</t>
+  </si>
+  <si>
+    <t>The system loads all orders within an acceptable time without errors.</t>
+  </si>
+  <si>
+    <t>TC_OH_007</t>
+  </si>
+  <si>
+    <t>Unauthorized access to orders</t>
+  </si>
+  <si>
+    <t>Open OpenCart
+User is NOT logged in</t>
+  </si>
+  <si>
+    <t>Verify unauthorized users cannot access order history</t>
+  </si>
+  <si>
+    <t>1. Open OpenCart without logging in.
+2. Try to access 'Your Orders' page directly via URL.</t>
+  </si>
+  <si>
+    <t>The system redirects to the login page or displays an authorization error.</t>
+  </si>
+  <si>
+    <t>TC_OH_008</t>
+  </si>
+  <si>
+    <t>Logout from Order History page</t>
+  </si>
+  <si>
+    <t>Verify user can log out from Order History</t>
+  </si>
+  <si>
+    <t>1. Navigate to 'Your Orders' page.
+2. Click on 'Logout' button.</t>
+  </si>
+  <si>
+    <t>The user is logged out and redirected to the homepage or login page.</t>
+  </si>
+  <si>
+    <t>TC_OH_009</t>
+  </si>
+  <si>
+    <t>Order History page layout on different browsers</t>
+  </si>
+  <si>
+    <t>Verify the Order History page renders correctly across different browsers</t>
+  </si>
+  <si>
+    <t>1. Open OpenCart in different browsers (Chrome, Firefox, Edge, Safari).
+2. Navigate to 'Your Orders' page.
+3. Verify that all elements (order list, filters, buttons) are displayed correctly.</t>
+  </si>
+  <si>
+    <t>The Order History page should render correctly across all tested browsers with no UI distortions.</t>
+  </si>
+  <si>
+    <t>TC_OH_010</t>
+  </si>
+  <si>
+    <t>Order History page responsiveness</t>
+  </si>
+  <si>
+    <t>Verify the page adjusts correctly on different screen sizes</t>
+  </si>
+  <si>
+    <t>1. Open OpenCart on different devices (PC, tablet, mobile).
+2. Navigate to 'Your Orders' page.
+3. Resize the browser window to different resolutions.
+4. Verify that the page elements adjust properly without overlapping or breaking.</t>
+  </si>
+  <si>
+    <t>The Order History page should be fully responsive and adapt to different screen sizes without layout issues.</t>
+  </si>
+  <si>
+    <t>TC_OH_011</t>
+  </si>
+  <si>
+    <t>Button and link functionality on Order History page</t>
+  </si>
+  <si>
+    <t>Verify all buttons and links function correctly</t>
+  </si>
+  <si>
+    <t>1. Navigate to 'Your Orders' page.
+2. Click on each button and link (e.g., 'Action', 'Back', 'Logout').
+3. Verify that each action performs the expected functionality.</t>
+  </si>
+  <si>
+    <t>All buttons and links should function correctly and navigate to the expected pages without errors.</t>
   </si>
 </sst>
 </file>
@@ -1757,24 +1912,11 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -1812,15 +1954,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1829,22 +1971,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1890,8 +2029,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2D91B3ED-BFB3-4BF6-B9E2-B45047E3BC66}" name="Tabelle1" displayName="Tabelle1" ref="A1:B22" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
-  <autoFilter ref="A1:B22" xr:uid="{2D91B3ED-BFB3-4BF6-B9E2-B45047E3BC66}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2D91B3ED-BFB3-4BF6-B9E2-B45047E3BC66}" name="Tabelle1" displayName="Tabelle1" ref="A1:B11" totalsRowShown="0" headerRowDxfId="3" dataDxfId="2">
+  <autoFilter ref="A1:B11" xr:uid="{2D91B3ED-BFB3-4BF6-B9E2-B45047E3BC66}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{AFD0C039-7F58-456D-9118-3E6C37D5AFFD}" name="Test Szenario auf Open Car+A1:B14t" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{22051654-053C-48DC-A251-B2AACFF72BDF}" name="Number of Test Cases" dataDxfId="0"/>
@@ -2163,7 +2302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D279CBF0-E909-4C39-954E-02A0B1FE8668}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.140625" customWidth="1"/>
@@ -2172,15 +2311,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>350</v>
+        <v>339</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="B2" s="2">
         <v>20</v>
@@ -2188,7 +2327,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="B3" s="2">
         <v>22</v>
@@ -2196,7 +2335,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="B4" s="2">
         <v>10</v>
@@ -2204,7 +2343,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>348</v>
+        <v>337</v>
       </c>
       <c r="B5" s="2">
         <v>22</v>
@@ -2212,7 +2351,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="B6" s="2">
         <v>9</v>
@@ -2246,79 +2385,15 @@
       <c r="A10" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="2"/>
-    </row>
-    <row r="17" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B17" s="2"/>
-    </row>
-    <row r="18" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
+      <c r="B10" s="2">
         <v>11</v>
       </c>
-      <c r="B18" s="2"/>
-    </row>
-    <row r="19" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="2"/>
-    </row>
-    <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="11" t="s">
-        <v>349</v>
-      </c>
-      <c r="B22" s="2">
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="B11" s="2">
         <v>3</v>
       </c>
     </row>
@@ -2331,91 +2406,357 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{884EF907-734D-47C2-A462-0A7DDD7773AA}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8E5B671-0B83-466E-B4C9-A5B4C2F32FB0}">
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="23.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" customWidth="1"/>
+    <col min="6" max="6" width="23.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="105" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="120" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="150" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="195" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="135" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>530</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8E5B671-0B83-466E-B4C9-A5B4C2F32FB0}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83B7116B-4DF8-4BB1-9D76-F6F969D5F7C7}">
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAAF1EEB-08B3-4462-A935-285A740C21B1}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB318571-7AA6-48E7-8B34-1554E4D4D71F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6366D9F1-B0C3-4E0E-A154-D57D8B3B5093}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD04566-2B9F-4B07-AA34-BF57464EB60D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E879D26-DF42-416A-B355-648FF3505B03}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2166216-EEEF-4E1B-B517-FAF39C77E32F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B3BDDD2-D55F-46D4-BF02-5AC4E8168912}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51240DEB-4720-4744-A3E5-ABE3B15218B8}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2435,565 +2776,422 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F321C8C-3303-4D7C-9741-9B98D2CB30B9}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D0881DA-FFFD-4EA2-A7CE-6EEFF29BDA2D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C6C93B5-A0D8-4D55-82E6-2C662B74A26E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62A08BA0-82AB-40C6-AB10-9C065EBEE794}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADC3A216-5155-4CEF-8A20-6800539D6F36}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83B7116B-4DF8-4BB1-9D76-F6F969D5F7C7}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" customWidth="1"/>
-    <col min="5" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="21.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="75" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>344</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -3016,462 +3214,462 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>144</v>
-      </c>
       <c r="F9" s="4" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>157</v>
-      </c>
       <c r="F13" s="4" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -3494,242 +3692,242 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
     </row>
     <row r="2" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
     </row>
     <row r="3" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
     <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
     </row>
     <row r="6" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
     </row>
     <row r="7" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
     <row r="9" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
     <row r="10" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
     <row r="11" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
@@ -3754,506 +3952,506 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="G1" s="7"/>
       <c r="H1" s="7"/>
     </row>
     <row r="2" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
     </row>
     <row r="3" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
     </row>
     <row r="4" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:8" ht="120" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
     </row>
     <row r="11" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:8" ht="135" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
     </row>
     <row r="18" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
     </row>
     <row r="20" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
     <row r="21" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
     </row>
     <row r="22" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
     </row>
     <row r="23" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
@@ -4278,202 +4476,202 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="165" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="135" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>312</v>
-      </c>
       <c r="E5" s="7" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="120" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
@@ -4496,242 +4694,242 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>390</v>
+        <v>379</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>391</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>392</v>
+        <v>381</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>395</v>
+        <v>384</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>397</v>
+        <v>386</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>398</v>
+        <v>387</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>399</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>389</v>
+        <v>378</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -4754,222 +4952,222 @@
   <sheetData>
     <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>356</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>357</v>
+        <v>346</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="165" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>368</v>
+        <v>357</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>371</v>
+        <v>360</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>372</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>374</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>375</v>
+        <v>364</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="105" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>351</v>
+        <v>340</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>377</v>
+        <v>366</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>378</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>363</v>
-      </c>
       <c r="D9" s="2" t="s">
-        <v>379</v>
+        <v>368</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>381</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>382</v>
+        <v>371</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>358</v>
+        <v>347</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>385</v>
+        <v>374</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>387</v>
+        <v>376</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>369</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -4992,222 +5190,222 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>438</v>
+        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>439</v>
+        <v>428</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>440</v>
+        <v>429</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>441</v>
+        <v>430</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>445</v>
+        <v>434</v>
       </c>
       <c r="C4" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>435</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>446</v>
-      </c>
       <c r="E4" s="7" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="105" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="150" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="135" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="165" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
